--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MISSOURI_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MISSOURI_2020.xlsx
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C50">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C96">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C109">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C148">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C155">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C163">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C251">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C392">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C406">
@@ -10003,7 +10003,7 @@
         <v>20</v>
       </c>
       <c r="D536">
-        <v>0.009267840593141797</v>
+        <v>0.009267840593141796</v>
       </c>
     </row>
     <row r="537">
